--- a/tame_output/ON/bt/strategyON_20240307.xlsx
+++ b/tame_output/ON/bt/strategyON_20240307.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,17 +1002,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>485.2%</t>
+          <t>476.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-87.4%</t>
+          <t>-84.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-114.8%</t>
+          <t>-118.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>79.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>73.5%</t>
+          <t>74.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-41.0%</t>
+          <t>-42.5%</t>
         </is>
       </c>
     </row>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-1.998344617850759</v>
+        <v>-2.371295868894057</v>
       </c>
       <c r="E1861" t="n">
-        <v>2.311242629234789</v>
+        <v>2.16206212881747</v>
       </c>
       <c r="F1861" t="n">
         <v>0.2704514200752166</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-1.996296032989048</v>
+        <v>-2.369247284032347</v>
       </c>
       <c r="E1862" t="n">
-        <v>2.318549623413714</v>
+        <v>2.169369122996395</v>
       </c>
       <c r="F1862" t="n">
         <v>0.272699120133409</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-1.99386896846033</v>
+        <v>-2.366820219503628</v>
       </c>
       <c r="E1863" t="n">
-        <v>2.318774964231033</v>
+        <v>2.169594463813714</v>
       </c>
       <c r="F1863" t="n">
         <v>0.2723663383262573</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-1.995160990234668</v>
+        <v>-2.368112241277966</v>
       </c>
       <c r="E1864" t="n">
-        <v>2.317019699536057</v>
+        <v>2.167839199118738</v>
       </c>
       <c r="F1864" t="n">
         <v>0.2710743165519193</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-1.99997558248951</v>
+        <v>-2.372926833532808</v>
       </c>
       <c r="E1865" t="n">
-        <v>2.310279295105581</v>
+        <v>2.161098794688262</v>
       </c>
       <c r="F1865" t="n">
         <v>0.2710743165519193</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-1.996818881459306</v>
+        <v>-2.369770132502604</v>
       </c>
       <c r="E1866" t="n">
-        <v>2.30953602612654</v>
+        <v>2.160355525709221</v>
       </c>
       <c r="F1866" t="n">
         <v>0.2710743165519193</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-2.000831913871827</v>
+        <v>-2.373783164915126</v>
       </c>
       <c r="E1867" t="n">
-        <v>2.31818950383021</v>
+        <v>2.169009003412891</v>
       </c>
       <c r="F1867" t="n">
         <v>0.2710743165519193</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-2.014546778196939</v>
+        <v>-2.387498029240237</v>
       </c>
       <c r="E1868" t="n">
-        <v>2.308803123245861</v>
+        <v>2.159622622828542</v>
       </c>
       <c r="F1868" t="n">
         <v>0.2710743165519193</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-2.020063698040905</v>
+        <v>-2.393014949084204</v>
       </c>
       <c r="E1869" t="n">
-        <v>2.305001275363275</v>
+        <v>2.155820774945956</v>
       </c>
       <c r="F1869" t="n">
         <v>0.2710743165519193</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-2.024876736506242</v>
+        <v>-2.39782798754954</v>
       </c>
       <c r="E1870" t="n">
-        <v>2.306855035906349</v>
+        <v>2.15767453548903</v>
       </c>
       <c r="F1870" t="n">
         <v>0.2695276818491334</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-2.022759577781949</v>
+        <v>-2.395710828825247</v>
       </c>
       <c r="E1871" t="n">
-        <v>2.303675594861663</v>
+        <v>2.154495094444344</v>
       </c>
       <c r="F1871" t="n">
         <v>0.2695276818491334</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-2.02228223120346</v>
+        <v>-2.395233482246757</v>
       </c>
       <c r="E1872" t="n">
-        <v>2.303764432171475</v>
+        <v>2.154583931754156</v>
       </c>
       <c r="F1872" t="n">
         <v>0.2695276818491334</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-2.021257444896602</v>
+        <v>-2.3942086959399</v>
       </c>
       <c r="E1873" t="n">
-        <v>2.306745862665648</v>
+        <v>2.157565362248329</v>
       </c>
       <c r="F1873" t="n">
         <v>0.270552468155991</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-2.039998825155521</v>
+        <v>-2.412950076198818</v>
       </c>
       <c r="E1874" t="n">
-        <v>2.304599613860131</v>
+        <v>2.155419113442812</v>
       </c>
       <c r="F1874" t="n">
         <v>0.270552468155991</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-2.052968167940619</v>
+        <v>-2.425919418983917</v>
       </c>
       <c r="E1875" t="n">
-        <v>2.307327896703269</v>
+        <v>2.158147396285949</v>
       </c>
       <c r="F1875" t="n">
         <v>0.2575831253708925</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-2.046492021147059</v>
+        <v>-2.419443272190357</v>
       </c>
       <c r="E1876" t="n">
-        <v>2.312960106042461</v>
+        <v>2.163779605625142</v>
       </c>
       <c r="F1876" t="n">
         <v>0.2640592721644521</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-2.042801096190648</v>
+        <v>-2.415752347233946</v>
       </c>
       <c r="E1877" t="n">
-        <v>2.314436476025026</v>
+        <v>2.165255975607707</v>
       </c>
       <c r="F1877" t="n">
         <v>0.2640592721644521</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-2.035585743318832</v>
+        <v>-2.40853699436213</v>
       </c>
       <c r="E1878" t="n">
-        <v>2.322835814292395</v>
+        <v>2.173655313875075</v>
       </c>
       <c r="F1878" t="n">
         <v>0.3338375074548339</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-1.984557897237006</v>
+        <v>-2.357509148280304</v>
       </c>
       <c r="E1879" t="n">
-        <v>2.347729507209561</v>
+        <v>2.198549006792242</v>
       </c>
       <c r="F1879" t="n">
         <v>0.4090468457619349</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-1.911088065569558</v>
+        <v>-2.284039316612856</v>
       </c>
       <c r="E1880" t="n">
-        <v>2.392489141369961</v>
+        <v>2.243308640952642</v>
       </c>
       <c r="F1880" t="n">
         <v>0.4825166774293833</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-1.830715710105628</v>
+        <v>-2.203666961148926</v>
       </c>
       <c r="E1881" t="n">
-        <v>2.43919330430305</v>
+        <v>2.290012803885731</v>
       </c>
       <c r="F1881" t="n">
         <v>0.5628890328933129</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-1.797783840292777</v>
+        <v>-2.170735091336076</v>
       </c>
       <c r="E1882" t="n">
-        <v>2.445146887326595</v>
+        <v>2.295966386909275</v>
       </c>
       <c r="F1882" t="n">
         <v>0.5628890328933129</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-1.817948481842325</v>
+        <v>-2.190899732885623</v>
       </c>
       <c r="E1883" t="n">
-        <v>2.4304088399328</v>
+        <v>2.28122833951548</v>
       </c>
       <c r="F1883" t="n">
         <v>0.5427243913437656</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-1.759281551820791</v>
+        <v>-2.13223280286409</v>
       </c>
       <c r="E1884" t="n">
-        <v>2.454991401779969</v>
+        <v>2.30581090136265</v>
       </c>
       <c r="F1884" t="n">
         <v>0.6276838597739033</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-1.696212319514452</v>
+        <v>-2.06916357055775</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.48291282333162</v>
+        <v>2.3337323229143</v>
       </c>
       <c r="F1885" t="n">
         <v>0.5991702970916688</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-1.644196805545639</v>
+        <v>-2.017148056588938</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.507709364605545</v>
+        <v>2.358528864188226</v>
       </c>
       <c r="F1886" t="n">
         <v>0.5991702970916688</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-1.468627136624735</v>
+        <v>-1.841578387668034</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.576462005275165</v>
+        <v>2.427281504857846</v>
       </c>
       <c r="F1887" t="n">
         <v>0.5991702970916688</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-1.271357730896737</v>
+        <v>-1.644308981940036</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.670423177731237</v>
+        <v>2.521242677313917</v>
       </c>
       <c r="F1888" t="n">
         <v>0.7964397028196669</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-1.072205623659637</v>
+        <v>-1.445156874702936</v>
       </c>
       <c r="E1889" t="n">
-        <v>2.737032886979394</v>
+        <v>2.587852386562074</v>
       </c>
       <c r="F1889" t="n">
         <v>0.9617622287694803</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-0.8463604709402264</v>
+        <v>-1.219311721983525</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.836950021103367</v>
+        <v>2.687769520686047</v>
       </c>
       <c r="F1890" t="n">
         <v>1.003688904356644</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-0.560085658617532</v>
+        <v>-0.9330369096608311</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.952599090588504</v>
+        <v>2.803418590171184</v>
       </c>
       <c r="F1891" t="n">
         <v>1.003688904356644</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-0.3332898315441981</v>
+        <v>-0.7062410825874972</v>
       </c>
       <c r="E1892" t="n">
-        <v>3.045951195579945</v>
+        <v>2.896770695162625</v>
       </c>
       <c r="F1892" t="n">
         <v>1.071802848978189</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-0.0493811006154492</v>
+        <v>-0.4223323516587483</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.165248392190081</v>
+        <v>3.016067891772761</v>
       </c>
       <c r="F1893" t="n">
         <v>1.071802848978189</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>0.1976061495775029</v>
+        <v>-0.1753451014657962</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.254306029873396</v>
+        <v>3.105125529456077</v>
       </c>
       <c r="F1894" t="n">
         <v>1.318790099171141</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.387626171097482</v>
+        <v>3.395410814385297</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>0.4679434563087082</v>
+        <v>0.4297567551692721</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.352557471252971</v>
+        <v>3.337282790797197</v>
       </c>
       <c r="F1895" t="n">
         <v>1.318790099171141</v>

--- a/tame_output/ON/bt/strategyON_20240307.xlsx
+++ b/tame_output/ON/bt/strategyON_20240307.xlsx
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-118.6%</t>
+          <t>-118.4%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-42.5%</t>
+          <t>-42.4%</t>
         </is>
       </c>
     </row>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>0.4297567551692721</v>
+        <v>0.4313213068780578</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.337282790797197</v>
+        <v>3.337908611480711</v>
       </c>
       <c r="F1895" t="n">
         <v>1.318790099171141</v>

--- a/tame_output/ON/bt/strategyON_20240307.xlsx
+++ b/tame_output/ON/bt/strategyON_20240307.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,32 +1002,32 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>476.6%</t>
+          <t>471.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-118.4%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-56.1%</t>
         </is>
       </c>
     </row>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>0.4313213068780578</v>
+        <v>0.08849176573827289</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.337908611480711</v>
+        <v>3.200776795024797</v>
       </c>
       <c r="F1895" t="n">
         <v>1.318790099171141</v>

--- a/tame_output/ON/bt/strategyON_20240307.xlsx
+++ b/tame_output/ON/bt/strategyON_20240307.xlsx
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.395410814385297</v>
+        <v>3.395410814385298</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
